--- a/artfynd/A 31738-2023 artfynd.xlsx
+++ b/artfynd/A 31738-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165902</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165781</v>
       </c>
       <c r="B3" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166010</v>
       </c>
       <c r="B4" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165780</v>
       </c>
       <c r="B5" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166123</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31738-2023 artfynd.xlsx
+++ b/artfynd/A 31738-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165902</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165781</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166010</v>
       </c>
       <c r="B4" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165780</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166123</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 31738-2023 artfynd.xlsx
+++ b/artfynd/A 31738-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129165781</v>
       </c>
       <c r="B3" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166010</v>
       </c>
       <c r="B4" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165780</v>
       </c>
       <c r="B5" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31738-2023 artfynd.xlsx
+++ b/artfynd/A 31738-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165902</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165781</v>
       </c>
       <c r="B3" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129166010</v>
       </c>
       <c r="B4" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129165780</v>
       </c>
       <c r="B5" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129166123</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
